--- a/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -315,7 +315,7 @@
 </t>
   </si>
   <si>
-    <t>Cette métadonnée représente l’identifiant du patient, en l’occurrence, le matricule INS (NIR ou NIA) du patient tel que défini dans le cadre juridique.</t>
+    <t>Cette métadonnée contient l'identifiant du patient tel que connu par les interlocuteurs prenant part à l'échange. Le matricule INS (NIR ou NIA) du patient doit être utilisé en priorité. À défaut de disponibilité de l'INS, un autre identifiant (ex: IPP du système émetteur) peut être utilisé.</t>
   </si>
   <si>
     <t>xdmSubmissionSet.sourceID</t>

--- a/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSubmissionSet.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="124">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -334,23 +334,58 @@
     <t>Identifiant unique global affecté à ce lot de soumission par son créateur. Cet attribut est utilisé à des fins de référence externe alors que entryUUID est destiné à des fins de gestion interne.</t>
   </si>
   <si>
-    <t>xdmSubmissionSet.contentTypeCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
+    <t>xdmSubmissionSet.contentType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmCode
 </t>
   </si>
   <si>
     <t>Ensemble de métadonnées représentant le type d’activité associé à l’événement clinique ayant abouti à la constitution du lot de soumission.</t>
   </si>
   <si>
-    <t>**Submission Set**</t>
-  </si>
-  <si>
     <t>preferred</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J03-XdsContentTypeCode-CISIS/FHIR/JDV-J03-XdsContentTypeCode-CISIS|20260223120000</t>
+  </si>
+  <si>
+    <t>xdmSubmissionSet.contentType.code</t>
+  </si>
+  <si>
+    <t>contentTypeCode correspondant au type d’activité associé à l’événement ayant abouti à la 
+constitution du lot de soumission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les valeurs possibles doivent être un code provenant du jeu de valeurs mis à disposition par le projet (exemple : JDV_J59_ContentTypeCode_DMP).
+  En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J03_XdsContentTypeCode_CISIS peut être utilisé. </t>
+  </si>
+  <si>
+    <t>xdmCode.code</t>
+  </si>
+  <si>
+    <t>xdmSubmissionSet.contentType.displayName</t>
+  </si>
+  <si>
+    <t>Libellé associé au contentTypeCode.</t>
+  </si>
+  <si>
+    <t>Libellé associé au code.</t>
+  </si>
+  <si>
+    <t>xdmCode.displayName</t>
+  </si>
+  <si>
+    <t>xdmSubmissionSet.contentType.codingScheme</t>
+  </si>
+  <si>
+    <t>OID du système de codage associé au code contentTypeCode.</t>
+  </si>
+  <si>
+    <t>OID du système de codage.</t>
+  </si>
+  <si>
+    <t>xdmCode.codingScheme</t>
   </si>
   <si>
     <t>xdmSubmissionSet.author</t>
@@ -361,18 +396,6 @@
   </si>
   <si>
     <t>Représente la personne physique ou morale et/ou le dispositif auteur d’un lot de soumission</t>
-  </si>
-  <si>
-    <t>xdmSubmissionSet.homeCommunityID</t>
-  </si>
-  <si>
-    <t>Cette métadonnée correspond à l’identifiant de la communauté représentée par le système cible si celui-ci offre des fonctionnalités de communication avec d’autres communautés telles que présentées dans le profil XCA d’IHE. Elle n’est pas utilisée par les transactions décrites dans ce volet.</t>
-  </si>
-  <si>
-    <t>xdmSubmissionSet.intendedRecipient</t>
-  </si>
-  <si>
-    <t>Cette métadonnée représente les destinataires (structure ou professionnel) auxquels lot de soumission est destiné. Elle n’est pas utilisée par les transactions décrites dans ce volet.</t>
   </si>
 </sst>
 </file>
@@ -674,11 +697,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -708,7 +731,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="31.65234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.98046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1756,7 +1779,7 @@
         <v>106</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1783,11 +1806,11 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -1822,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1848,13 +1871,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1905,7 +1928,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -1933,7 +1956,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
@@ -1948,13 +1971,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>114</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2005,10 +2028,10 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>79</v>
@@ -2022,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2033,10 +2056,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2048,13 +2071,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2105,18 +2128,118 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>73</v>
       </c>
     </row>
